--- a/docs/downloads/经营分_津河省区__唐山南片区_2026-10-19.xlsx
+++ b/docs/downloads/经营分_津河省区__唐山南片区_2026-10-19.xlsx
@@ -12,7 +12,7 @@
     <sheet name="匹配异常" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'匹配异常'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -936,24 +936,20 @@
           <t>唐山南片区</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>唐山市</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>6601149467607435268</t>
+          <t>7421035070742104115</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7天优品（唐山市小山人民医院店）</t>
+          <t>维也纳国际酒店(唐山火车站新华西路店)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7天优品酒店(唐山人民医院小山店)</t>
+          <t>维也纳国际酒店(唐山火车站新华西路店)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -962,42 +958,42 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N5" t="n">
         <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P5" t="n">
         <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
         <v>30</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T5" t="n">
         <v>20</v>
@@ -1031,43 +1027,43 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>7232543592244316172</t>
+          <t>6601149467607435268</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0唐山滦南建设路店）</t>
+          <t>7天优品（唐山市小山人民医院店）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0唐山滦南建设路店)</t>
+          <t>7天优品酒店(唐山人民医院小山店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N6" t="n">
         <v>30</v>
@@ -1079,7 +1075,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R6" t="n">
         <v>30</v>
@@ -1119,22 +1115,22 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>6601172037241161732</t>
+          <t>7232543592244316172</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>麗枫酒店·唐山火车站店</t>
+          <t>维也纳酒店（5.0唐山滦南建设路店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>丽枫酒店(唐山火车站店)</t>
+          <t>维也纳酒店(5.0唐山滦南建设路店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1207,29 +1203,29 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7310824642271250470</t>
+          <t>6601172037241161732</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>麗枫酒店唐山乐亭京唐港店</t>
+          <t>麗枫酒店·唐山火车站店</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>麗枫酒店(唐山乐亭京唐港店)</t>
+          <t>丽枫酒店(唐山火车站店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>87</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1249,13 +1245,13 @@
         <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
         <v>30</v>
@@ -1295,29 +1291,29 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>6713650905083840516</t>
+          <t>7310824642271250470</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>麗枫酒店（唐山师范学院会展中心店）</t>
+          <t>麗枫酒店唐山乐亭京唐港店</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>麗枫酒店(唐山师范学院会展中心店)</t>
+          <t>麗枫酒店(唐山乐亭京唐港店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>87</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1337,13 +1333,13 @@
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P9" t="n">
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1376,20 +1372,24 @@
           <t>唐山南片区</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>唐山市</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7302345968501032979</t>
+          <t>6713650905083840516</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>喆啡酒店（唐山海港龙泽国际店）</t>
+          <t>麗枫酒店（唐山师范学院会展中心店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>喆啡酒店(唐山海港龙泽国际店)</t>
+          <t>麗枫酒店(唐山师范学院会展中心店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
@@ -1460,24 +1460,20 @@
           <t>唐山南片区</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>唐山市</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7319360898227767315</t>
+          <t>7302345968501032979</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>希岸酒店唐山火车站南湖景区店</t>
+          <t>喆啡酒店（唐山海港龙泽国际店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>希岸酒店(唐山火车站南湖景区店)</t>
+          <t>喆啡酒店(唐山海港龙泽国际店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1489,7 +1485,7 @@
         <v>92</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1509,13 +1505,13 @@
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P11" t="n">
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1548,20 +1544,24 @@
           <t>唐山南片区</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>唐山市</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7298589904819193867</t>
+          <t>7319360898227767315</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>希岸酒店（唐山曹妃甸工业区店）</t>
+          <t>希岸酒店唐山火车站南湖景区店</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>希岸酒店(唐山曹妃甸港站店)</t>
+          <t>希岸酒店(唐山火车站南湖景区店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1593,13 +1593,13 @@
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P12" t="n">
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
         <v>30</v>
@@ -1632,24 +1632,20 @@
           <t>唐山南片区</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>唐山市</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7377243108003547147</t>
+          <t>7298589904819193867</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（5.0版唐山会展远洋城旗舰店）</t>
+          <t>希岸酒店（唐山曹妃甸工业区店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(5.0版唐山会展远洋城旗舰店)</t>
+          <t>希岸酒店(唐山曹妃甸港站店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1681,13 +1677,13 @@
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
@@ -1727,17 +1723,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6601137101670975502</t>
+          <t>7377243108003547147</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>维也纳酒店唐山南湖旅游景区万达广场店</t>
+          <t>维也纳国际酒店（5.0版唐山会展远洋城旗舰店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>维也纳酒店(唐山南湖旅游景区店)</t>
+          <t>维也纳国际酒店(5.0版唐山会展远洋城旗舰店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1815,22 +1811,22 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7599791338866870312</t>
+          <t>6601137101670975502</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>维也纳酒店（唐山爱琴海店）</t>
+          <t>维也纳酒店唐山南湖旅游景区万达广场店</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>维也纳酒店(唐山爱琴海太阳城店)</t>
+          <t>维也纳酒店(唐山南湖旅游景区店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1903,26 +1899,26 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6976840350027483149</t>
+          <t>7599791338866870312</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7天优品酒店（唐山路北区韩城职业技术学院店）</t>
+          <t>维也纳酒店（唐山爱琴海店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7天优品酒店(唐山路北区韩城职业技术学院店)</t>
+          <t>维也纳酒店(唐山爱琴海太阳城店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1939,13 +1935,13 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P16" t="n">
         <v>30</v>
@@ -1991,17 +1987,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7317832777913600036</t>
+          <t>6976840350027483149</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>麗枫酒店唐山曹妃甸工业区店</t>
+          <t>7天优品酒店（唐山路北区韩城职业技术学院店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>丽枫酒店(唐山曹妃甸工业区店)</t>
+          <t>7天优品酒店(唐山路北区韩城职业技术学院店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2027,13 +2023,13 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
+        <v>20</v>
+      </c>
+      <c r="N17" t="n">
+        <v>30</v>
+      </c>
+      <c r="O17" t="n">
         <v>25</v>
-      </c>
-      <c r="N17" t="n">
-        <v>30</v>
-      </c>
-      <c r="O17" t="n">
-        <v>20</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
@@ -2079,17 +2075,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7280417745231939596</t>
+          <t>7317832777913600036</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>维也纳国际（5.0版唐山海港文化大街店）</t>
+          <t>麗枫酒店唐山曹妃甸工业区店</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>维也纳国际(唐山海港文化大街店)</t>
+          <t>丽枫酒店(唐山曹妃甸工业区店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2098,36 +2094,36 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>搭门店,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2167,17 +2163,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7405478165960722495</t>
+          <t>7280417745231939596</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>锦江之星（滦南县北河公园酒店）</t>
+          <t>维也纳国际（5.0版唐山海港文化大街店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>锦江之星酒店(滦南县北河公园店)</t>
+          <t>维也纳国际(唐山海港文化大街店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2193,7 +2189,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>搭门店,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2203,19 +2199,19 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2255,55 +2251,55 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7234809474035222568</t>
+          <t>7405478165960722495</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>喆啡酒店唐山滦南县建设路店</t>
+          <t>锦江之星（滦南县北河公园酒店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>喆啡酒店(唐山滦南县建设路店)</t>
+          <t>锦江之星酒店(滦南县北河公园店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P20" t="n">
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2343,26 +2339,26 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7547899350207170603</t>
+          <t>7234809474035222568</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>希岸DELUXE酒店唐山南湖公园妇幼保健院店</t>
+          <t>喆啡酒店唐山滦南县建设路店</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>希岸Deluxe酒店(唐山南湖景区·唐山宴店)</t>
+          <t>喆啡酒店(唐山滦南县建设路店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2391,7 +2387,7 @@
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2431,17 +2427,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7367614056108132403</t>
+          <t>7547899350207170603</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>喆啡酒店河北唐山曹妃甸工业区店</t>
+          <t>希岸DELUXE酒店唐山南湖公园妇幼保健院店</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>喆啡酒店</t>
+          <t>希岸Deluxe酒店(唐山南湖景区·唐山宴店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2450,10 +2446,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2467,7 +2463,7 @@
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
@@ -2519,17 +2515,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7469664745855911947</t>
+          <t>7367614056108132403</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>喆啡酒店（唐山火车站路南区政府店）</t>
+          <t>喆啡酒店河北唐山曹妃甸工业区店</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>喆啡酒店(唐山火车站路南区政府店)</t>
+          <t>喆啡酒店</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2538,14 +2534,14 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2555,7 +2551,7 @@
         <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N23" t="n">
         <v>30</v>
@@ -2607,17 +2603,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7362772394882123812</t>
+          <t>7469664745855911947</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>麗枫酒店唐山曹妃甸揽月湾理工大学店</t>
+          <t>喆啡酒店（唐山火车站路南区政府店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>丽枫酒店(唐山曹妃甸新区理工大学店)</t>
+          <t>喆啡酒店(唐山火车站路南区政府店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2629,7 +2625,7 @@
         <v>110</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2695,79 +2691,167 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
+          <t>7362772394882123812</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>麗枫酒店唐山曹妃甸揽月湾理工大学店</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>丽枫酒店(唐山曹妃甸新区理工大学店)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>已认证</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>110</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>拿收益</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>10</v>
+      </c>
+      <c r="L25" t="n">
+        <v>10</v>
+      </c>
+      <c r="M25" t="n">
+        <v>30</v>
+      </c>
+      <c r="N25" t="n">
+        <v>30</v>
+      </c>
+      <c r="O25" t="n">
+        <v>30</v>
+      </c>
+      <c r="P25" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>20</v>
+      </c>
+      <c r="R25" t="n">
+        <v>30</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="n">
+        <v>20</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>7249997748999555075</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>汇通百达网络科技（上海）有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>津河省区</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>唐山南片区</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>唐山市</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
           <t>7581341806999111721</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>维也纳酒店（唐山河头老街店）</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>维也纳酒店(河头老街店)</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>已认证</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="H26" t="n">
         <v>112</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>7</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>稳房源</t>
         </is>
       </c>
-      <c r="K25" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" t="n">
-        <v>10</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="K26" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" t="n">
+        <v>10</v>
+      </c>
+      <c r="M26" t="n">
         <v>22</v>
       </c>
-      <c r="N25" t="n">
-        <v>30</v>
-      </c>
-      <c r="O25" t="n">
-        <v>30</v>
-      </c>
-      <c r="P25" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>30</v>
-      </c>
-      <c r="R25" t="n">
-        <v>30</v>
-      </c>
-      <c r="S25" t="n">
-        <v>20</v>
-      </c>
-      <c r="T25" t="n">
-        <v>20</v>
-      </c>
-      <c r="U25" t="inlineStr">
+      <c r="N26" t="n">
+        <v>30</v>
+      </c>
+      <c r="O26" t="n">
+        <v>30</v>
+      </c>
+      <c r="P26" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>30</v>
+      </c>
+      <c r="R26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="n">
+        <v>20</v>
+      </c>
+      <c r="U26" t="inlineStr">
         <is>
           <t>7249997748999555075</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>汇通百达网络科技（上海）有限公司</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V25"/>
-  <conditionalFormatting sqref="H2:H25">
+  <autoFilter ref="A1:V26"/>
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2779,7 +2863,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I25">
+  <conditionalFormatting sqref="I2:I26">
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
